--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_47.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3323584.018036684</v>
+        <v>3316642.830206838</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10041900.99034356</v>
+        <v>10030081.59640417</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10041900.99034356</v>
+        <v>10030081.59640417</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162899666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162899666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12662287.91809872</v>
+        <v>12662707.85709989</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>32.58699138541447</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -781,10 +781,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S3" t="n">
-        <v>296.3577706585854</v>
+        <v>295.3577706585853</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -845,7 +845,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>119.040440756494</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>32.58699138541447</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S6" t="n">
-        <v>333.9365645502421</v>
+        <v>386</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1033,7 +1033,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>385</v>
+        <v>331.9365645502421</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70619138541446</v>
+        <v>32.58699138541447</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1210,16 +1210,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>300.9629961541974</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>106.4200609560755</v>
       </c>
     </row>
     <row r="10">
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172477</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>62.67776252544257</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T12" t="n">
         <v>55.35776521751382</v>
@@ -1620,10 +1620,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>58.00965870352741</v>
+        <v>65.85585008894192</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1699,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>195.5513766340942</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>197.2737972923793</v>
@@ -1738,7 +1738,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U15" t="n">
-        <v>289.8088571951495</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V15" t="n">
         <v>64.51066719152016</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V17" t="n">
-        <v>283.8164155522384</v>
+        <v>279.8510241668239</v>
       </c>
       <c r="W17" t="n">
         <v>288.3734759809475</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>62.67776252544263</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>197.2737972923793</v>
@@ -1978,7 +1978,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V18" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
         <v>82.37314290982852</v>
@@ -1987,7 +1987,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>288.9898902010971</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2088,13 +2088,13 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G20" t="n">
         <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
-        <v>58.00965870352741</v>
+        <v>65.85585008894192</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2161,10 +2161,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>70.00566530353007</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2209,10 +2209,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>118.0355277429562</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U21" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V21" t="n">
         <v>64.51066719152016</v>
@@ -2331,10 +2331,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>65.85585008894192</v>
       </c>
       <c r="I23" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U24" t="n">
-        <v>289.8088571951495</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V24" t="n">
         <v>64.51066719152016</v>
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>144.8481678023229</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
@@ -2686,10 +2686,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U27" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V27" t="n">
-        <v>127.1884297169626</v>
+        <v>127.1884297169628</v>
       </c>
       <c r="W27" t="n">
         <v>82.37314290982852</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>7.846191385414608</v>
       </c>
       <c r="S29" t="n">
         <v>144.8481678023229</v>
@@ -2875,10 +2875,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>73.04152018756581</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>197.2737972923793</v>
@@ -2923,7 +2923,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U30" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V30" t="n">
         <v>64.51066719152016</v>
@@ -3045,7 +3045,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>144.8481678023229</v>
@@ -3109,7 +3109,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>70.00566530352997</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>197.2737972923793</v>
+        <v>267.2794625959094</v>
       </c>
       <c r="S33" t="n">
         <v>116.5639999646113</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>7.846191385414608</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3352,10 +3352,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>73.04152018756567</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V36" t="n">
         <v>64.51066719152016</v>
@@ -3409,7 +3409,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.846191385414608</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3561,7 +3561,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>242.2818334606677</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S39" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900539</v>
       </c>
       <c r="T39" t="n">
         <v>55.35776521751382</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900539</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3984,7 +3984,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G44" t="n">
         <v>53.75737228701621</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4105,16 +4105,16 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169627</v>
       </c>
       <c r="W45" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>69.86273944538755</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>145.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>95.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>85.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>80.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>75.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>71.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>63.79615291456007</v>
       </c>
       <c r="I2" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J2" t="n">
-        <v>411.95</v>
+        <v>413.02</v>
       </c>
       <c r="K2" t="n">
-        <v>411.95</v>
+        <v>413.02</v>
       </c>
       <c r="L2" t="n">
-        <v>411.95</v>
+        <v>413.02</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>413.02</v>
       </c>
       <c r="N2" t="n">
-        <v>411.95</v>
+        <v>795.1600000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>777.6999999999999</v>
+        <v>1177.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1544</v>
       </c>
       <c r="Q2" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="R2" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1448.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1259.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>1007.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>775.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>534.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>340.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>228.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="C3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="D3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="I3" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J3" t="n">
-        <v>154.756520175299</v>
+        <v>154.8365201752989</v>
       </c>
       <c r="K3" t="n">
-        <v>343.9493362696824</v>
+        <v>344.0293362696823</v>
       </c>
       <c r="L3" t="n">
-        <v>615.2997978648825</v>
+        <v>615.3797978648824</v>
       </c>
       <c r="M3" t="n">
-        <v>701.3803396077418</v>
+        <v>701.4603396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>834.6606242153101</v>
+        <v>834.74062421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1073.703075899029</v>
+        <v>1073.783075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1011.404879873102</v>
+        <v>1011.484879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>622.5159909842129</v>
+        <v>621.5858899741118</v>
       </c>
       <c r="S3" t="n">
-        <v>323.1647074906923</v>
+        <v>323.2447074906922</v>
       </c>
       <c r="T3" t="n">
-        <v>317.7528234325975</v>
+        <v>317.8328234325975</v>
       </c>
       <c r="U3" t="n">
-        <v>317.5403388263483</v>
+        <v>317.6203388263482</v>
       </c>
       <c r="V3" t="n">
-        <v>302.8830992389542</v>
+        <v>302.9630992389542</v>
       </c>
       <c r="W3" t="n">
-        <v>270.182954885592</v>
+        <v>270.262954885592</v>
       </c>
       <c r="X3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="Y3" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1247.586867406406</v>
+        <v>1024.653690076604</v>
       </c>
       <c r="C4" t="n">
-        <v>1373.588873224842</v>
+        <v>1150.65569589504</v>
       </c>
       <c r="D4" t="n">
-        <v>1373.588873224842</v>
+        <v>1182.916259347549</v>
       </c>
       <c r="E4" t="n">
-        <v>1373.588873224842</v>
+        <v>1182.916259347549</v>
       </c>
       <c r="F4" t="n">
-        <v>1373.588873224842</v>
+        <v>1182.916259347549</v>
       </c>
       <c r="G4" t="n">
-        <v>1373.588873224842</v>
+        <v>1182.916259347549</v>
       </c>
       <c r="H4" t="n">
-        <v>1373.588873224842</v>
+        <v>1182.916259347549</v>
       </c>
       <c r="I4" t="n">
-        <v>1540</v>
+        <v>1182.916259347549</v>
       </c>
       <c r="J4" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="K4" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1520.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1398.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1225.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>982.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>692.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>363.0938962980761</v>
       </c>
       <c r="R4" t="n">
-        <v>30.8</v>
+        <v>33.19275692317598</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>33.19275692317598</v>
       </c>
       <c r="T4" t="n">
-        <v>256.125934252978</v>
+        <v>33.19275692317598</v>
       </c>
       <c r="U4" t="n">
-        <v>502.6771268912646</v>
+        <v>279.7439495614626</v>
       </c>
       <c r="V4" t="n">
-        <v>701.4985197772105</v>
+        <v>478.5653424474086</v>
       </c>
       <c r="W4" t="n">
-        <v>873.3894380368879</v>
+        <v>650.456260707086</v>
       </c>
       <c r="X4" t="n">
-        <v>1024.420229061081</v>
+        <v>801.4870517312795</v>
       </c>
       <c r="Y4" t="n">
-        <v>1135.829529740114</v>
+        <v>912.8963524103118</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>145.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>95.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>85.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>80.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>75.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>71.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>63.79615291456007</v>
       </c>
       <c r="I5" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="K5" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="L5" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="M5" t="n">
-        <v>411.95</v>
+        <v>413.02</v>
       </c>
       <c r="N5" t="n">
-        <v>793.0999999999999</v>
+        <v>795.16</v>
       </c>
       <c r="O5" t="n">
-        <v>1174.25</v>
+        <v>1177.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1174.25</v>
+        <v>1177.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="R5" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.197616982083</v>
+        <v>1448.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.636423316867</v>
+        <v>1259.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1007.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>775.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>534.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>340.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>228.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="H6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="I6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J6" t="n">
-        <v>154.756520175299</v>
+        <v>154.8365201752989</v>
       </c>
       <c r="K6" t="n">
-        <v>343.9493362696824</v>
+        <v>344.0293362696823</v>
       </c>
       <c r="L6" t="n">
-        <v>615.2997978648825</v>
+        <v>615.3797978648824</v>
       </c>
       <c r="M6" t="n">
-        <v>701.3803396077418</v>
+        <v>701.4603396077417</v>
       </c>
       <c r="N6" t="n">
-        <v>834.6606242153101</v>
+        <v>834.74062421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1073.703075899029</v>
+        <v>1073.783075899029</v>
       </c>
       <c r="P6" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>797.3435314796468</v>
+        <v>796.4134304695458</v>
       </c>
       <c r="S6" t="n">
-        <v>460.0338703177861</v>
+        <v>406.5144405705559</v>
       </c>
       <c r="T6" t="n">
-        <v>454.6219862596914</v>
+        <v>401.1025565124611</v>
       </c>
       <c r="U6" t="n">
-        <v>454.4095016534421</v>
+        <v>400.8900719062119</v>
       </c>
       <c r="V6" t="n">
-        <v>439.752262066048</v>
+        <v>386.2328323188178</v>
       </c>
       <c r="W6" t="n">
-        <v>50.86337317715914</v>
+        <v>50.94337317715914</v>
       </c>
       <c r="X6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>341.3787305522381</v>
+        <v>229.7013928859459</v>
       </c>
       <c r="C7" t="n">
-        <v>467.3807363706738</v>
+        <v>229.7013928859459</v>
       </c>
       <c r="D7" t="n">
-        <v>580.6998804956739</v>
+        <v>343.020537010946</v>
       </c>
       <c r="E7" t="n">
-        <v>698.528784707087</v>
+        <v>460.8494412223591</v>
       </c>
       <c r="F7" t="n">
-        <v>822.8897572990224</v>
+        <v>585.2104138142946</v>
       </c>
       <c r="G7" t="n">
-        <v>976.2963231859077</v>
+        <v>738.6169797011798</v>
       </c>
       <c r="H7" t="n">
-        <v>1145.812908345305</v>
+        <v>908.1335648605774</v>
       </c>
       <c r="I7" t="n">
-        <v>1366.945787281388</v>
+        <v>1129.26644379666</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1490.350184449112</v>
       </c>
       <c r="K7" t="n">
-        <v>1540</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="L7" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.901760089168</v>
       </c>
       <c r="M7" t="n">
-        <v>1394.364404484516</v>
+        <v>1396.05164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.137430115194</v>
       </c>
       <c r="O7" t="n">
-        <v>978.5758798878493</v>
+        <v>980.2631229646734</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.9117115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7811393749001</v>
       </c>
       <c r="R7" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="V7" t="n">
-        <v>229.621392885946</v>
+        <v>229.7013928859459</v>
       </c>
       <c r="W7" t="n">
-        <v>229.621392885946</v>
+        <v>229.7013928859459</v>
       </c>
       <c r="X7" t="n">
-        <v>229.621392885946</v>
+        <v>229.7013928859459</v>
       </c>
       <c r="Y7" t="n">
-        <v>229.621392885946</v>
+        <v>229.7013928859459</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.4463380542246</v>
+        <v>145.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>91.47201659665494</v>
+        <v>95.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>81.02842494024101</v>
+        <v>85.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>76.62106170097975</v>
+        <v>80.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>71.68204280399807</v>
+        <v>75.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>67.88671726155745</v>
+        <v>71.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>59.79615291456007</v>
+        <v>63.79615291456007</v>
       </c>
       <c r="I8" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>397.5800000000002</v>
       </c>
       <c r="K8" t="n">
-        <v>411.95</v>
+        <v>397.5800000000002</v>
       </c>
       <c r="L8" t="n">
-        <v>411.95</v>
+        <v>397.5800000000002</v>
       </c>
       <c r="M8" t="n">
-        <v>793.1</v>
+        <v>779.7200000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>1174.25</v>
+        <v>1161.86</v>
       </c>
       <c r="O8" t="n">
-        <v>1174.25</v>
+        <v>1161.86</v>
       </c>
       <c r="P8" t="n">
-        <v>1174.25</v>
+        <v>1161.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="R8" t="n">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="S8" t="n">
-        <v>1444.193769896644</v>
+        <v>1448.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1255.632576231427</v>
+        <v>1259.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>1003.893892848992</v>
+        <v>1007.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>771.7211411653319</v>
+        <v>775.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>530.9398522956878</v>
+        <v>534.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>336.7157780929932</v>
+        <v>340.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>224.2739268982392</v>
+        <v>228.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>897.189519579215</v>
+        <v>614.9469680170382</v>
       </c>
       <c r="C9" t="n">
-        <v>897.189519579215</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="D9" t="n">
-        <v>897.189519579215</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="E9" t="n">
-        <v>593.1864931608338</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="F9" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="G9" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="H9" t="n">
-        <v>250.1195817084329</v>
+        <v>250.1995817084329</v>
       </c>
       <c r="I9" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="J9" t="n">
-        <v>154.756520175299</v>
+        <v>154.8365201752989</v>
       </c>
       <c r="K9" t="n">
-        <v>343.9493362696824</v>
+        <v>344.0293362696823</v>
       </c>
       <c r="L9" t="n">
-        <v>615.2997978648825</v>
+        <v>615.3797978648824</v>
       </c>
       <c r="M9" t="n">
-        <v>701.3803396077418</v>
+        <v>701.4603396077417</v>
       </c>
       <c r="N9" t="n">
-        <v>834.6606242153101</v>
+        <v>834.74062421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1073.703075899029</v>
+        <v>1073.783075899029</v>
       </c>
       <c r="P9" t="n">
-        <v>1186.232420368536</v>
+        <v>1186.312420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.484879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.471008962092</v>
+        <v>862.723468466658</v>
       </c>
       <c r="S9" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4871048660406</v>
       </c>
       <c r="T9" t="n">
-        <v>964.8227613033797</v>
+        <v>790.0752208079458</v>
       </c>
       <c r="U9" t="n">
-        <v>964.6102766971304</v>
+        <v>789.8627362016965</v>
       </c>
       <c r="V9" t="n">
-        <v>949.9530371097363</v>
+        <v>775.2054966143024</v>
       </c>
       <c r="W9" t="n">
-        <v>917.2528927563742</v>
+        <v>742.5053522609403</v>
       </c>
       <c r="X9" t="n">
-        <v>897.189519579215</v>
+        <v>722.4419790837811</v>
       </c>
       <c r="Y9" t="n">
-        <v>897.189519579215</v>
+        <v>614.9469680170382</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>404.0685093339829</v>
+        <v>1247.666867406406</v>
       </c>
       <c r="C10" t="n">
-        <v>530.0705151524187</v>
+        <v>1373.668873224841</v>
       </c>
       <c r="D10" t="n">
-        <v>643.3896592774188</v>
+        <v>1486.988017349842</v>
       </c>
       <c r="E10" t="n">
-        <v>761.2185634888318</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="F10" t="n">
-        <v>885.5795360807673</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="G10" t="n">
-        <v>1038.986101967653</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="H10" t="n">
-        <v>1208.50268712705</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="I10" t="n">
-        <v>1429.635566063133</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063133</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="K10" t="n">
-        <v>1540.000000000002</v>
+        <v>1541.687243076824</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1517.901760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1396.05164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1223.137430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>980.2631229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>689.8317115219688</v>
+        <v>689.9117115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393749001</v>
+        <v>360.7811393749001</v>
       </c>
       <c r="R10" t="n">
-        <v>30.8</v>
+        <v>30.88</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>68.13025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>30.8</v>
+        <v>256.205934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>30.8</v>
+        <v>502.7571268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>30.8</v>
+        <v>701.5785197772105</v>
       </c>
       <c r="W10" t="n">
-        <v>30.8</v>
+        <v>873.4694380368879</v>
       </c>
       <c r="X10" t="n">
-        <v>180.9018709886585</v>
+        <v>1024.500229061081</v>
       </c>
       <c r="Y10" t="n">
-        <v>292.3111716676908</v>
+        <v>1135.909529740114</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I11" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O11" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q11" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R11" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>119.3229040110726</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="H12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J12" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L12" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M12" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N12" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O12" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P12" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>647.3506049216877</v>
+        <v>647.4306049216879</v>
       </c>
       <c r="S12" t="n">
-        <v>466.2983195781991</v>
+        <v>529.6891908160198</v>
       </c>
       <c r="T12" t="n">
-        <v>410.3813850150538</v>
+        <v>473.7722562528746</v>
       </c>
       <c r="U12" t="n">
-        <v>359.6638499037541</v>
+        <v>423.0547211415748</v>
       </c>
       <c r="V12" t="n">
-        <v>294.5015598113094</v>
+        <v>357.8924310491302</v>
       </c>
       <c r="W12" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6872361907176</v>
       </c>
       <c r="X12" t="n">
-        <v>140.7279412706871</v>
+        <v>204.1188125085079</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>154.2285167851399</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C13" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D13" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E13" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F13" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G13" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H13" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I13" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J13" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K13" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L13" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M13" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N13" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O13" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P13" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q13" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R13" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S13" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>380.3468717970915</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W13" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X13" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I14" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>733.1420762183976</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>733.1420762183976</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>1243.990904947333</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="N14" t="n">
-        <v>1797.400904947332</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S14" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.93203277325181</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="F15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="G15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="H15" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="I15" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J15" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M15" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N15" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O15" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S15" t="n">
-        <v>708.3170038559392</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T15" t="n">
-        <v>652.400069292794</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U15" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V15" t="n">
-        <v>294.5015598113094</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W15" t="n">
-        <v>211.2963649528968</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X15" t="n">
-        <v>140.7279412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y15" t="n">
-        <v>90.8376455473191</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>870.0458296400257</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C16" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D16" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F16" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G16" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H16" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I16" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J16" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K16" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L16" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M16" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N16" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O16" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P16" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q16" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R16" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S16" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V16" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W16" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X16" t="n">
-        <v>745.8791912947012</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y16" t="n">
-        <v>807.7884919737335</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I17" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="K17" t="n">
-        <v>436.0291130376557</v>
+        <v>736.1520762183974</v>
       </c>
       <c r="L17" t="n">
-        <v>733.1420762183976</v>
+        <v>736.1520762183974</v>
       </c>
       <c r="M17" t="n">
-        <v>1243.990904947333</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="N17" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q17" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R17" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S17" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.93203277325181</v>
+        <v>119.3229040110727</v>
       </c>
       <c r="C18" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="D18" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J18" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M18" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N18" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O18" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P18" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S18" t="n">
-        <v>708.3170038559392</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T18" t="n">
-        <v>652.400069292794</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U18" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V18" t="n">
-        <v>536.5202440890496</v>
+        <v>357.8924310491303</v>
       </c>
       <c r="W18" t="n">
-        <v>453.3150492306369</v>
+        <v>274.6872361907176</v>
       </c>
       <c r="X18" t="n">
-        <v>382.7466255484273</v>
+        <v>204.118812508508</v>
       </c>
       <c r="Y18" t="n">
-        <v>90.8376455473191</v>
+        <v>154.22851678514</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F19" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G19" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H19" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I19" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J19" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K19" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L19" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M19" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N19" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O19" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P19" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q19" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R19" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S19" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I20" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>736.1520762183974</v>
       </c>
       <c r="L20" t="n">
-        <v>436.0291130376557</v>
+        <v>736.1520762183974</v>
       </c>
       <c r="M20" t="n">
-        <v>946.8779417665908</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="N20" t="n">
-        <v>1500.287941766591</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q20" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>390.9334315372855</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J21" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L21" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N21" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O21" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T21" t="n">
-        <v>763.9167385504074</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U21" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V21" t="n">
-        <v>294.5015598113094</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W21" t="n">
-        <v>211.2963649528968</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C22" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D22" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E22" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F22" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G22" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H22" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I22" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J22" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K22" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L22" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M22" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N22" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O22" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P22" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q22" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R22" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S22" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T22" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U22" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V22" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W22" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X22" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y22" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I23" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="K23" t="n">
-        <v>436.0291130376557</v>
+        <v>620.3511712710648</v>
       </c>
       <c r="L23" t="n">
-        <v>436.0291130376557</v>
+        <v>1174.751171271065</v>
       </c>
       <c r="M23" t="n">
-        <v>946.8779417665908</v>
+        <v>1685.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1500.287941766591</v>
+        <v>2240</v>
       </c>
       <c r="O23" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="Q23" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J24" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N24" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O24" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P24" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>826.0584179616072</v>
+        <v>937.6550872192207</v>
       </c>
       <c r="S24" t="n">
-        <v>708.3170038559392</v>
+        <v>819.9136731135527</v>
       </c>
       <c r="T24" t="n">
-        <v>652.400069292794</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U24" t="n">
-        <v>359.6638499037541</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V24" t="n">
-        <v>294.5015598113094</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>211.2963649528968</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>140.7279412706871</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>90.8376455473191</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>870.0458296400257</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>946.5478354584615</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D25" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E25" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F25" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H25" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J25" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K25" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L25" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M25" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N25" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O25" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P25" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q25" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R25" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S25" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W25" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X25" t="n">
-        <v>745.8791912947012</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y25" t="n">
-        <v>807.7884919737335</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H26" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I26" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J26" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>989.4391130376558</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>1286.552076218397</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="M26" t="n">
-        <v>1797.400904947332</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="N26" t="n">
-        <v>1797.400904947332</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q26" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R26" t="n">
-        <v>2231.994554156147</v>
+        <v>2240</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J27" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L27" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M27" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N27" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O27" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P27" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>529.6091908160197</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T27" t="n">
-        <v>473.6922562528744</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U27" t="n">
-        <v>422.9747211415747</v>
+        <v>423.0547211415749</v>
       </c>
       <c r="V27" t="n">
-        <v>294.5015598113094</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>211.2963649528968</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>140.7279412706871</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>90.8376455473191</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C28" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D28" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E28" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F28" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G28" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H28" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I28" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J28" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K28" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L28" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M28" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N28" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O28" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P28" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q28" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R28" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S28" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T28" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U28" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W28" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X28" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y28" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C29" t="n">
-        <v>332.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>271.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E29" t="n">
-        <v>217.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F29" t="n">
-        <v>161.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I29" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J29" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K29" t="n">
-        <v>598.13</v>
+        <v>44.8</v>
       </c>
       <c r="L29" t="n">
-        <v>690.5809049473327</v>
+        <v>44.8</v>
       </c>
       <c r="M29" t="n">
-        <v>690.5809049473327</v>
+        <v>555.648828728935</v>
       </c>
       <c r="N29" t="n">
-        <v>690.5809049473327</v>
+        <v>1110.048828728935</v>
       </c>
       <c r="O29" t="n">
-        <v>1243.990904947333</v>
+        <v>1664.448828728935</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q29" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R29" t="n">
-        <v>2236</v>
+        <v>2232.074554156147</v>
       </c>
       <c r="S29" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T29" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U29" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V29" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W29" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X29" t="n">
-        <v>729.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y29" t="n">
-        <v>566.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55.93203277325181</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C30" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D30" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E30" t="n">
-        <v>44.72</v>
+        <v>387.8669114524009</v>
       </c>
       <c r="F30" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H30" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I30" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J30" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L30" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M30" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N30" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O30" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P30" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>937.5750872192207</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>819.8336731135527</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T30" t="n">
-        <v>763.9167385504074</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U30" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V30" t="n">
-        <v>294.5015598113094</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W30" t="n">
-        <v>211.2963649528968</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X30" t="n">
-        <v>140.7279412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y30" t="n">
-        <v>90.8376455473191</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C31" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D31" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E31" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F31" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H31" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I31" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J31" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K31" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L31" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M31" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N31" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O31" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P31" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q31" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R31" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S31" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T31" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U31" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V31" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W31" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X31" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y31" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C32" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E32" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I32" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J32" t="n">
-        <v>179.7320762183976</v>
+        <v>44.8</v>
       </c>
       <c r="K32" t="n">
-        <v>179.7320762183976</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="L32" t="n">
-        <v>733.1420762183976</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="M32" t="n">
-        <v>1243.990904947333</v>
+        <v>692.6009049473324</v>
       </c>
       <c r="N32" t="n">
-        <v>1797.400904947332</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="O32" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q32" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R32" t="n">
-        <v>2231.994554156147</v>
+        <v>2240</v>
       </c>
       <c r="S32" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>472.7782575464261</v>
+        <v>402.1454643105373</v>
       </c>
       <c r="C33" t="n">
-        <v>461.5662247731743</v>
+        <v>390.9334315372855</v>
       </c>
       <c r="D33" t="n">
-        <v>390.8534315372855</v>
+        <v>390.9334315372855</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J33" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L33" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M33" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N33" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O33" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>1000.885958457041</v>
+        <v>930.2531652211525</v>
       </c>
       <c r="S33" t="n">
-        <v>883.1445443513733</v>
+        <v>812.5117511154845</v>
       </c>
       <c r="T33" t="n">
-        <v>827.2276097882281</v>
+        <v>756.5948165523392</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5100746769283</v>
+        <v>705.8772814410395</v>
       </c>
       <c r="V33" t="n">
-        <v>711.3477845844836</v>
+        <v>640.7149913485948</v>
       </c>
       <c r="W33" t="n">
-        <v>628.142589726071</v>
+        <v>557.5097964901822</v>
       </c>
       <c r="X33" t="n">
-        <v>557.5741660438614</v>
+        <v>486.9413728079726</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.6838703204934</v>
+        <v>437.0510770846046</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C34" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D34" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F34" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G34" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H34" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I34" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J34" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K34" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L34" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M34" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N34" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O34" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P34" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q34" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R34" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S34" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T34" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V34" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W34" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X34" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y34" t="n">
-        <v>815.4992746459407</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J35" t="n">
-        <v>436.0291130376557</v>
+        <v>44.8</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>599.2</v>
       </c>
       <c r="L35" t="n">
-        <v>436.0291130376557</v>
+        <v>1153.6</v>
       </c>
       <c r="M35" t="n">
-        <v>946.8779417665908</v>
+        <v>1153.6</v>
       </c>
       <c r="N35" t="n">
-        <v>946.8779417665908</v>
+        <v>1685.6</v>
       </c>
       <c r="O35" t="n">
-        <v>1243.990904947333</v>
+        <v>2240</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="Q35" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2232.074554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="E36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="F36" t="n">
-        <v>118.4993133207734</v>
+        <v>44.8</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J36" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K36" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L36" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M36" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N36" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O36" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P36" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>713.2792034391077</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>648.1169133466631</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>564.9117184882504</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>494.3432948060407</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J37" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K37" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L37" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M37" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N37" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O37" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P37" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q37" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R37" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S37" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>946.8779417665908</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N38" t="n">
-        <v>946.8779417665908</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>2055.757941766591</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2055.757941766591</v>
       </c>
       <c r="Q38" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2232.074554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.2429040110725</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.8</v>
       </c>
       <c r="D39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.8</v>
       </c>
       <c r="E39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.8</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J39" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K39" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L39" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M39" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N39" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O39" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P39" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>647.4306049216879</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>466.3783195781991</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>154.1485167851398</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K40" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L40" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M40" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N40" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O40" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P40" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R40" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S40" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>181.7520762183975</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>736.1520762183975</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>1290.552076218397</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665908</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.2429040110725</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C42" t="n">
-        <v>108.0308712378206</v>
+        <v>44.8</v>
       </c>
       <c r="D42" t="n">
-        <v>108.0308712378206</v>
+        <v>44.8</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J42" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M42" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N42" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O42" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>647.3506049216877</v>
+        <v>647.4306049216879</v>
       </c>
       <c r="S42" t="n">
-        <v>529.6091908160197</v>
+        <v>466.3783195781991</v>
       </c>
       <c r="T42" t="n">
-        <v>473.6922562528744</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U42" t="n">
-        <v>422.9747211415747</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V42" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>274.6072361907174</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>204.0388125085078</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.1485167851397</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C43" t="n">
-        <v>954.2586181306687</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D43" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H43" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K43" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L43" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M43" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N43" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O43" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P43" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q43" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R43" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S43" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I44" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J44" t="n">
-        <v>179.7320762183977</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>179.7320762183977</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>179.7320762183977</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M44" t="n">
-        <v>690.5809049473327</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N44" t="n">
-        <v>690.5809049473327</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O44" t="n">
-        <v>1243.990904947333</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J45" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M45" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N45" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O45" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U45" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V45" t="n">
-        <v>294.5015598113094</v>
+        <v>648.1169133466631</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P46" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R46" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S46" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>420.0430062450903</v>
+        <v>421.0430062450903</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>863.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>439.6923140185368</v>
+        <v>456.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>385.2870600406814</v>
+        <v>370.6911004447217</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>930.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>863.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>456.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>542.2671287719298</v>
+        <v>543.2267247315259</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>405.4470466491309</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423173</v>
+        <v>930.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>863.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>542.2671287719298</v>
+        <v>558.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8687,10 +8687,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>370.3619737970638</v>
+        <v>373.3215697566601</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>300.1141042229715</v>
+        <v>560</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8924,10 +8924,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>373.3215697566599</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>173.3784367687241</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L17" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>70.24786957409245</v>
@@ -9389,7 +9389,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>303.0737001825673</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -9398,10 +9398,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>56.40782571081238</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,10 +9863,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>300.1141042229713</v>
+        <v>560</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,7 +9875,7 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>373.3215697566599</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
@@ -10100,22 +10100,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>93.38475247205326</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>559.2870600406815</v>
+        <v>138.6224905643152</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10334,22 +10334,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>171.4188408091283</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="L32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P32" t="n">
         <v>0.2870600406814136</v>
@@ -10571,28 +10571,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>559.9999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>1014.622695443573</v>
       </c>
       <c r="O35" t="n">
-        <v>370.361973797064</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10820,16 +10820,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>370.361973797064</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>358.9257734521414</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,22 +11045,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>173.3784367687242</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>171.4188408091284</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11294,13 +11294,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>373.3215697566601</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5911706460559</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646054422</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>779297.7385953129</v>
+        <v>779366.9743259861</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1503417.578631639</v>
+        <v>1503508.772517228</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2227537.418667966</v>
+        <v>2227650.57070847</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2959905.515041027</v>
+        <v>2960018.667081531</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3684047.31323227</v>
+        <v>3684160.465272774</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4408189.11142351</v>
+        <v>4408302.263464016</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5132330.909614749</v>
+        <v>5132444.061655255</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5856472.707805989</v>
+        <v>5856585.859846494</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6580614.505997228</v>
+        <v>6580727.658037733</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7304756.304188468</v>
+        <v>7304869.456228972</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8028898.10237971</v>
+        <v>8029011.254420217</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8753039.900570957</v>
+        <v>8753153.052611463</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9477181.698762204</v>
+        <v>9477294.85080271</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10201323.49695345</v>
+        <v>10201436.64899396</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10925465.2951447</v>
+        <v>10925578.4471852</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1479723.15137858</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="C2" t="n">
-        <v>1479723.151378579</v>
+        <v>1479768.022390798</v>
       </c>
       <c r="D2" t="n">
-        <v>1479723.15137858</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="E2" t="n">
         <v>1479768.022390799</v>
@@ -26302,16 +26302,16 @@
         <v>1479768.022390799</v>
       </c>
       <c r="M2" t="n">
+        <v>1479768.022390799</v>
+      </c>
+      <c r="N2" t="n">
         <v>1479768.022390798</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1479768.022390799</v>
       </c>
       <c r="O2" t="n">
         <v>1479768.022390799</v>
       </c>
       <c r="P2" t="n">
-        <v>1479768.022390799</v>
+        <v>1479768.022390798</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135520</v>
+        <v>135872</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>415520</v>
+        <v>415872</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572326.3960678478</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570269.0362327076</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568208.8854605397</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544712.0690347301</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542769.8864290807</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540825.0236843044</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538877.4615810197</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>536927.1806494284</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>534974.161164563</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983396</v>
+        <v>533018.3831414287</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531059.8263300107</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529098.4702101597</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527134.2939863527</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525167.2765823142</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523197.3966354961</v>
       </c>
     </row>
     <row r="5">
@@ -26425,49 +26425,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57035.6</v>
+        <v>57096.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>57035.6</v>
+        <v>57096.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>57035.6</v>
+        <v>57096.39999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="F5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="G5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="H5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="I5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="J5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="K5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="L5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="M5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="N5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="O5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="P5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>716253.426479071</v>
+        <v>714473.2263229513</v>
       </c>
       <c r="C6" t="n">
-        <v>853831.4066128846</v>
+        <v>852402.5861580909</v>
       </c>
       <c r="D6" t="n">
-        <v>855892.1785252012</v>
+        <v>854462.7369302589</v>
       </c>
       <c r="E6" t="n">
-        <v>532014.6191642639</v>
+        <v>530335.8033560688</v>
       </c>
       <c r="F6" t="n">
-        <v>875205.5145097676</v>
+        <v>873525.9859617179</v>
       </c>
       <c r="G6" t="n">
-        <v>877151.0909779532</v>
+        <v>875470.8487064944</v>
       </c>
       <c r="H6" t="n">
-        <v>879099.3677952545</v>
+        <v>877418.4108097792</v>
       </c>
       <c r="I6" t="n">
-        <v>881050.3644386149</v>
+        <v>879368.6917413705</v>
       </c>
       <c r="J6" t="n">
-        <v>467484.1006402402</v>
+        <v>465449.7112262358</v>
       </c>
       <c r="K6" t="n">
-        <v>884960.5963924594</v>
+        <v>883277.4892493699</v>
       </c>
       <c r="L6" t="n">
-        <v>886919.8719527191</v>
+        <v>885236.0460607882</v>
       </c>
       <c r="M6" t="n">
-        <v>827633.9478486978</v>
+        <v>825949.4021806392</v>
       </c>
       <c r="N6" t="n">
-        <v>890846.8448835521</v>
+        <v>889161.5784044454</v>
       </c>
       <c r="O6" t="n">
-        <v>612814.5841412897</v>
+        <v>611128.5958084847</v>
       </c>
       <c r="P6" t="n">
-        <v>894785.1869922999</v>
+        <v>893098.4757553024</v>
       </c>
     </row>
   </sheetData>
@@ -26859,49 +26859,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -26972,13 +26972,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>350</v>
@@ -26993,7 +26993,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -27005,7 +27005,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -27014,7 +27014,7 @@
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27030,7 +27030,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27042,7 +27042,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27057,7 +27057,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -27066,7 +27066,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -27076,34 +27076,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27115,10 +27115,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27317,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>117.4941682972701</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27560,10 +27560,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>162.2737972923793</v>
+        <v>161.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>170.2062293060259</v>
+        <v>171.206229306026</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27597,7 +27597,7 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>318.1226457853627</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27612,10 +27612,10 @@
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>344.7255028677531</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>117.4941682972701</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27797,10 +27797,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>162.2737972923793</v>
+        <v>161.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>132.6274354143692</v>
+        <v>80.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>47.37314290982852</v>
+        <v>100.4365783595864</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>98.59195770635561</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>340.3763885766103</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>121.3749682972702</v>
+        <v>117.4941682972701</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27989,16 +27989,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>41.70910106771527</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>292.9713318100589</v>
       </c>
     </row>
     <row r="10">
@@ -28074,25 +28074,25 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>336.2326479955248</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>399.061696933803</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28241,7 +28241,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28274,7 +28274,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T12" t="n">
         <v>350</v>
@@ -28362,13 +28362,13 @@
         <v>350</v>
       </c>
       <c r="V13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W13" t="n">
         <v>350</v>
       </c>
       <c r="X13" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="Y13" t="n">
         <v>350</v>
@@ -28399,10 +28399,10 @@
         <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28478,10 +28478,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523269</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>350</v>
@@ -28517,7 +28517,7 @@
         <v>350</v>
       </c>
       <c r="U15" t="n">
-        <v>110.4015025650372</v>
+        <v>350</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -28542,7 +28542,7 @@
         <v>350</v>
       </c>
       <c r="C16" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="D16" t="n">
         <v>350</v>
@@ -28596,7 +28596,7 @@
         <v>350</v>
       </c>
       <c r="U16" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="V16" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28678,7 +28678,7 @@
         <v>350</v>
       </c>
       <c r="V17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="W17" t="n">
         <v>350</v>
@@ -28712,7 +28712,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>263.0617733495847</v>
       </c>
       <c r="H18" t="n">
         <v>332.1680871864211</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>350</v>
@@ -28757,7 +28757,7 @@
         <v>350</v>
       </c>
       <c r="V18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>350</v>
@@ -28766,7 +28766,7 @@
         <v>350</v>
       </c>
       <c r="Y18" t="n">
-        <v>110.4015025650372</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28867,13 +28867,13 @@
         <v>350</v>
       </c>
       <c r="F20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G20" t="n">
         <v>350</v>
       </c>
       <c r="H20" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28940,10 +28940,10 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>277.9320215941726</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -28988,10 +28988,10 @@
         <v>350</v>
       </c>
       <c r="T21" t="n">
-        <v>287.3222374745577</v>
+        <v>350</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V21" t="n">
         <v>350</v>
@@ -29067,7 +29067,7 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29110,10 +29110,10 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="I23" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29216,19 +29216,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>110.4015025650372</v>
+        <v>350</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -29262,7 +29262,7 @@
         <v>350</v>
       </c>
       <c r="F25" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="G25" t="n">
         <v>350</v>
@@ -29310,7 +29310,7 @@
         <v>350</v>
       </c>
       <c r="V25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W25" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
         <v>350</v>
@@ -29456,7 +29456,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
@@ -29465,10 +29465,10 @@
         <v>350</v>
       </c>
       <c r="U27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>287.3222374745576</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="W27" t="n">
         <v>350</v>
@@ -29541,7 +29541,7 @@
         <v>350</v>
       </c>
       <c r="T28" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U28" t="n">
         <v>350</v>
@@ -29553,7 +29553,7 @@
         <v>350</v>
       </c>
       <c r="X28" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="Y28" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>243.0324074428798</v>
       </c>
       <c r="S29" t="n">
         <v>350</v>
@@ -29654,10 +29654,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343468</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>325.7395358750273</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>110.4015025650371</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>350</v>
@@ -29702,7 +29702,7 @@
         <v>350</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V30" t="n">
         <v>350</v>
@@ -29778,13 +29778,13 @@
         <v>350</v>
       </c>
       <c r="T31" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U31" t="n">
         <v>350</v>
       </c>
       <c r="V31" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W31" t="n">
         <v>350</v>
@@ -29824,7 +29824,7 @@
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>350</v>
@@ -29888,7 +29888,7 @@
         <v>350</v>
       </c>
       <c r="D33" t="n">
-        <v>277.9320215941727</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -29930,7 +29930,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>350</v>
+        <v>279.9943346964699</v>
       </c>
       <c r="S33" t="n">
         <v>350</v>
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="C34" t="n">
         <v>350</v>
@@ -30018,7 +30018,7 @@
         <v>350</v>
       </c>
       <c r="U34" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="V34" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>243.0324074428798</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30131,10 +30131,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>252.6980156874617</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30176,7 +30176,7 @@
         <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -30188,7 +30188,7 @@
         <v>350</v>
       </c>
       <c r="Y36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30267,7 +30267,7 @@
         <v>350</v>
       </c>
       <c r="Y37" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
     </row>
     <row r="38">
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>243.0324074428798</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30340,7 +30340,7 @@
         <v>350</v>
       </c>
       <c r="W38" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X38" t="n">
         <v>350</v>
@@ -30368,7 +30368,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>276.9584798124344</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30404,10 +30404,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="T39" t="n">
         <v>350</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>350</v>
       </c>
       <c r="J40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K40" t="n">
         <v>350</v>
@@ -30492,7 +30492,7 @@
         <v>350</v>
       </c>
       <c r="U40" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="V40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30602,7 +30602,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>279.9943346964702</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
@@ -30644,7 +30644,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30763,7 +30763,7 @@
         <v>350</v>
       </c>
       <c r="F44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G44" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30884,16 +30884,16 @@
         <v>350</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="W45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34755,16 +34755,16 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="O2" t="n">
-        <v>369.4444444444443</v>
+        <v>386</v>
       </c>
       <c r="P2" t="n">
-        <v>385</v>
+        <v>370.4040404040402</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34883,7 +34883,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>32.58642772980721</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -34898,10 +34898,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>168.0920472476348</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34989,19 +34989,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O5" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>369.4444444444445</v>
+        <v>370.4040404040405</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35138,10 +35138,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>63.32300887044785</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>51.85561477546729</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385</v>
+        <v>370.4040404040406</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35226,10 +35226,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N8" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>369.4444444444445</v>
+        <v>386</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35360,25 +35360,25 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>55.25174315856829</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>151.6180515036955</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35466,10 +35466,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O11" t="n">
-        <v>300.1141042229714</v>
+        <v>303.0737001825676</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35648,13 +35648,13 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V13" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W13" t="n">
         <v>123.6271901612903</v>
       </c>
       <c r="X13" t="n">
-        <v>102.5563545698924</v>
+        <v>94.7676852040268</v>
       </c>
       <c r="Y13" t="n">
         <v>62.53464715053764</v>
@@ -35694,7 +35694,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>300.1141042229715</v>
+        <v>560</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -35703,10 +35703,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>303.0737001825674</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35828,7 +35828,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C16" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608974</v>
       </c>
       <c r="D16" t="n">
         <v>64.46378194444452</v>
@@ -35882,7 +35882,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U16" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V16" t="n">
         <v>150.8296897837838</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>138.3354305236337</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L17" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36168,7 +36168,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>303.0737001825673</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -36177,10 +36177,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O20" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O23" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36548,7 +36548,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F25" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639244</v>
       </c>
       <c r="G25" t="n">
         <v>104.95612715847</v>
@@ -36596,7 +36596,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W25" t="n">
         <v>123.6271901612903</v>
@@ -36642,10 +36642,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>300.1141042229713</v>
+        <v>560</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,7 +36654,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>303.0737001825674</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U28" t="n">
         <v>199.0416087255421</v>
@@ -36839,7 +36839,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X28" t="n">
-        <v>102.5563545698924</v>
+        <v>94.7676852040268</v>
       </c>
       <c r="Y28" t="n">
         <v>62.53464715053764</v>
@@ -36879,22 +36879,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>93.38475247205326</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P29" t="n">
-        <v>559</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -37064,13 +37064,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U31" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V31" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W31" t="n">
         <v>123.6271901612903</v>
@@ -37113,22 +37113,22 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="L32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C34" t="n">
         <v>77.27475335195533</v>
@@ -37304,7 +37304,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U34" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596764</v>
       </c>
       <c r="V34" t="n">
         <v>150.8296897837838</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>559.9999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>537.3737373737374</v>
       </c>
       <c r="O35" t="n">
-        <v>300.1141042229716</v>
+        <v>560</v>
       </c>
       <c r="P35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37553,7 +37553,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>62.53464715053764</v>
+        <v>54.74597778467206</v>
       </c>
     </row>
     <row r="38">
@@ -37599,16 +37599,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O38" t="n">
-        <v>300.1141042229716</v>
+        <v>560</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>186.1030891246559</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
         <v>61.47922619885696</v>
@@ -37778,7 +37778,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596764</v>
       </c>
       <c r="V40" t="n">
         <v>150.8296897837838</v>
@@ -37824,22 +37824,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -38073,13 +38073,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>303.0737001825676</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
